--- a/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,16 @@
           <t>2026-06-21</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -493,6 +503,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,6 +523,11 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>flipkart</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1-GENZ</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1-GENZ</t>
+          <t>1-GENZ 2-STAR</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,16 +449,6 @@
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -503,16 +493,6 @@
           <t>Seema</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Prabhu</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Seema</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,11 +503,6 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>flipkart</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1-GENZ 2-STAR</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,16 @@
           <t>2026-06-21</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -493,6 +503,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -673,6 +693,23 @@
         </is>
       </c>
       <c r="I14" t="inlineStr">
+        <is>
+          <t>1-GENZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Track Pant</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>shopsy</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>1-GENZ</t>
         </is>

--- a/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,16 @@
           <t>2026-07-08</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -513,6 +523,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -540,6 +560,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>2-FADE 5-IND</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1-STAR</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,16 @@
           <t>2026-07-09</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -533,6 +543,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -737,6 +757,23 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>1-GENZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Track Pant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1-STAR</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1-STAR</t>
+          <t>2-STAR</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/dist/release/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,16 @@
           <t>2026-07-18</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -553,6 +563,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -774,6 +794,23 @@
       <c r="O16" t="inlineStr">
         <is>
           <t>2-STAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>White-Baggy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1-STAR</t>
         </is>
       </c>
     </row>
